--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-SyntheseMedicaleSejour.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-SyntheseMedicaleSejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-05T15:38:56+00:00</t>
+    <t>2025-10-06T12:29:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
